--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.59021792511999</v>
+        <v>10.495910412832</v>
       </c>
       <c r="D2" t="n">
-        <v>65.370463029493</v>
+        <v>10.62270024229261</v>
       </c>
       <c r="E2" t="n">
-        <v>11.20549640527014</v>
+        <v>1.820893165856397</v>
       </c>
       <c r="F2" t="n">
-        <v>12.96565077788271</v>
+        <v>2.106918251405941</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.09113957127402</v>
+        <v>4.077310180332028</v>
       </c>
       <c r="D3" t="n">
-        <v>17.0697602108858</v>
+        <v>2.773836034268943</v>
       </c>
       <c r="E3" t="n">
-        <v>11.20549640527014</v>
+        <v>1.820893165856397</v>
       </c>
       <c r="F3" t="n">
-        <v>12.96565077788271</v>
+        <v>2.106918251405941</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.14944935674681</v>
+        <v>6.361785520471358</v>
       </c>
       <c r="D4" t="n">
-        <v>36.82609865878643</v>
+        <v>5.984241032052795</v>
       </c>
       <c r="E4" t="n">
-        <v>11.20549640527014</v>
+        <v>1.820893165856397</v>
       </c>
       <c r="F4" t="n">
-        <v>12.96565077788271</v>
+        <v>2.106918251405941</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.3410897003817</v>
+        <v>4.117927076312026</v>
       </c>
       <c r="D5" t="n">
-        <v>23.53024615698653</v>
+        <v>3.823665000510311</v>
       </c>
       <c r="E5" t="n">
-        <v>11.20549640527014</v>
+        <v>1.820893165856397</v>
       </c>
       <c r="F5" t="n">
-        <v>12.96565077788271</v>
+        <v>2.106918251405941</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.2390623099524</v>
+        <v>6.051347625367265</v>
       </c>
       <c r="D6" t="n">
-        <v>34.51760346294197</v>
+        <v>5.609110562728071</v>
       </c>
       <c r="E6" t="n">
-        <v>11.20549640527014</v>
+        <v>1.820893165856397</v>
       </c>
       <c r="F6" t="n">
-        <v>12.96565077788271</v>
+        <v>2.106918251405941</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.39780940478813</v>
+        <v>6.727144028278071</v>
       </c>
       <c r="D7" t="n">
-        <v>38.76452705022909</v>
+        <v>6.299235645662227</v>
       </c>
       <c r="E7" t="n">
-        <v>11.20549640527014</v>
+        <v>1.820893165856397</v>
       </c>
       <c r="F7" t="n">
-        <v>12.96565077788271</v>
+        <v>2.106918251405941</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.09790613692165</v>
+        <v>7.490909747249768</v>
       </c>
       <c r="D8" t="n">
-        <v>44.56294225450212</v>
+        <v>7.241478116356594</v>
       </c>
       <c r="E8" t="n">
-        <v>11.20549640527014</v>
+        <v>1.820893165856397</v>
       </c>
       <c r="F8" t="n">
-        <v>12.96565077788271</v>
+        <v>2.106918251405941</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.98605342840928</v>
+        <v>6.660233682116508</v>
       </c>
       <c r="D9" t="n">
-        <v>40.1086289767567</v>
+        <v>6.517652208722963</v>
       </c>
       <c r="E9" t="n">
-        <v>11.20549640527014</v>
+        <v>1.820893165856397</v>
       </c>
       <c r="F9" t="n">
-        <v>12.96565077788271</v>
+        <v>2.106918251405941</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>46.67601520964686</v>
+        <v>7.584852471567616</v>
       </c>
       <c r="D10" t="n">
-        <v>45.5376876362547</v>
+        <v>7.399874240891388</v>
       </c>
       <c r="E10" t="n">
-        <v>11.20549640527014</v>
+        <v>1.820893165856397</v>
       </c>
       <c r="F10" t="n">
-        <v>12.96565077788271</v>
+        <v>2.106918251405941</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
